--- a/product_selector_out/STM32F427-437.xlsx
+++ b/product_selector_out/STM32F427-437.xlsx
@@ -11837,7 +11837,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13245,7 +13245,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F427-437.xlsx
+++ b/product_selector_out/STM32F427-437.xlsx
@@ -7142,9 +7142,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -8153,9 +8153,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -8827,9 +8827,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -9838,9 +9838,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="8" t="inlineStr">
@@ -10849,9 +10849,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">

--- a/product_selector_out/STM32F427-437.xlsx
+++ b/product_selector_out/STM32F427-437.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO26"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.51171875" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -4714,6 +4771,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -5051,6 +5113,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -5388,6 +5455,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -5725,6 +5797,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -6062,12 +6139,17 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6090,12 +6172,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6110,9 +6194,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -6163,7 +6246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO26"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6233,6 +6316,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6576,6 +6660,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6673,6 +6762,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7005,7 +7095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7342,7 +7437,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7679,7 +7779,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8016,7 +8121,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8353,7 +8463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8690,7 +8805,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9027,7 +9147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9364,7 +9489,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9701,7 +9831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10038,7 +10173,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10375,7 +10515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10712,7 +10857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11049,7 +11199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11386,7 +11541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11723,7 +11883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11731,8 +11896,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
